--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134859681</v>
+        <v>135495306</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>92608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576054</v>
+        <v>576050</v>
       </c>
       <c r="R2" t="n">
-        <v>6407792</v>
+        <v>6407748</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök, stubbe</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,38 +788,38 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134859681</t>
+          <t>https://artportalen.se/Sighting/135495306</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135046379</v>
+        <v>135495326</v>
       </c>
       <c r="B3" t="n">
-        <v>58141</v>
+        <v>92608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,13 +827,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576240</v>
+        <v>576075</v>
       </c>
       <c r="R3" t="n">
-        <v>6407794</v>
+        <v>6407830</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,38 +902,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046379</t>
+          <t>https://artportalen.se/Sighting/135495326</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135046394</v>
+        <v>135495368</v>
       </c>
       <c r="B4" t="n">
-        <v>58141</v>
+        <v>92608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,13 +941,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576213</v>
+        <v>576055</v>
       </c>
       <c r="R4" t="n">
-        <v>6407847</v>
+        <v>6407752</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,6 +1015,577 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495368</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135495421</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 28505, Dröppstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576007</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6407765</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495421</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135495438</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 28505, Dröppstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576019</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6407759</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495438</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134859681</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 28505, Dröppstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576054</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6407792</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosök, stubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134859681</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135046379</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 28505, Dröppstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576240</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6407794</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046379</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135046394</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 28505, Dröppstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576213</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6407847</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135046394</t>
         </is>
@@ -1026,6 +1596,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495306</v>
       </c>
       <c r="B2" t="n">
-        <v>92608</v>
+        <v>92610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>135495326</v>
       </c>
       <c r="B3" t="n">
-        <v>92608</v>
+        <v>92610</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135495368</v>
       </c>
       <c r="B4" t="n">
-        <v>92608</v>
+        <v>92610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>135495421</v>
       </c>
       <c r="B5" t="n">
-        <v>92608</v>
+        <v>92610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135495438</v>
       </c>
       <c r="B6" t="n">
-        <v>92608</v>
+        <v>92610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495306</v>
       </c>
       <c r="B2" t="n">
-        <v>92610</v>
+        <v>92625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>135495326</v>
       </c>
       <c r="B3" t="n">
-        <v>92610</v>
+        <v>92625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135495368</v>
       </c>
       <c r="B4" t="n">
-        <v>92610</v>
+        <v>92625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>135495421</v>
       </c>
       <c r="B5" t="n">
-        <v>92610</v>
+        <v>92625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135495438</v>
       </c>
       <c r="B6" t="n">
-        <v>92610</v>
+        <v>92625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495306</v>
       </c>
       <c r="B2" t="n">
-        <v>92625</v>
+        <v>92626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>135495326</v>
       </c>
       <c r="B3" t="n">
-        <v>92625</v>
+        <v>92626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135495368</v>
       </c>
       <c r="B4" t="n">
-        <v>92625</v>
+        <v>92626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>135495421</v>
       </c>
       <c r="B5" t="n">
-        <v>92625</v>
+        <v>92626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135495438</v>
       </c>
       <c r="B6" t="n">
-        <v>92625</v>
+        <v>92626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
